--- a/tools/config-xlsx/skill.xlsx
+++ b/tools/config-xlsx/skill.xlsx
@@ -442,7 +442,7 @@
         <v>attackCount</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="str">
         <v>aoe</v>
@@ -454,7 +454,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         <v>timer</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="str">
         <v>nearest</v>
@@ -483,7 +483,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/tools/config-xlsx/skill.xlsx
+++ b/tools/config-xlsx/skill.xlsx
@@ -425,7 +425,7 @@
         <v>maxTargets</v>
       </c>
       <c r="I1" t="str">
-        <v>dmgMult</v>
+        <v>effects</v>
       </c>
     </row>
     <row r="2">
@@ -453,8 +453,8 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2">
-        <v>0.5</v>
+      <c r="I2" t="str">
+        <v>damage:0.5</v>
       </c>
     </row>
     <row r="3">
@@ -482,8 +482,8 @@
       <c r="H3">
         <v>3</v>
       </c>
-      <c r="I3">
-        <v>1.2</v>
+      <c r="I3" t="str">
+        <v>damage:1.2</v>
       </c>
     </row>
     <row r="4">
@@ -511,8 +511,8 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4">
-        <v>2.5</v>
+      <c r="I4" t="str">
+        <v>damage:2.5</v>
       </c>
     </row>
   </sheetData>

--- a/tools/config-xlsx/skill.xlsx
+++ b/tools/config-xlsx/skill.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,6 +427,9 @@
       <c r="I1" t="str">
         <v>effects</v>
       </c>
+      <c r="J1" t="str">
+        <v>delivery</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -456,6 +459,9 @@
       <c r="I2" t="str">
         <v>damage:0.5</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -485,6 +491,9 @@
       <c r="I3" t="str">
         <v>damage:1.2</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -514,10 +523,13 @@
       <c r="I4" t="str">
         <v>damage:2.5</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/config-xlsx/skill.xlsx
+++ b/tools/config-xlsx/skill.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:N5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,25 +410,37 @@
         <v>cls</v>
       </c>
       <c r="D1" t="str">
+        <v>kind</v>
+      </c>
+      <c r="E1" t="str">
         <v>trigger</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>triggerValue</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>target</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>radius</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>maxTargets</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>effects</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>delivery</v>
+      </c>
+      <c r="L1" t="str">
+        <v>passiveTrigger</v>
+      </c>
+      <c r="M1" t="str">
+        <v>chance</v>
+      </c>
+      <c r="N1" t="str">
+        <v>targetMode</v>
       </c>
     </row>
     <row r="2">
@@ -442,94 +454,174 @@
         <v>dps</v>
       </c>
       <c r="D2" t="str">
+        <v>active</v>
+      </c>
+      <c r="E2" t="str">
         <v>attackCount</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>10</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>aoe</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>220</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="I2" t="str">
-        <v>damage:0.5</v>
-      </c>
       <c r="J2" t="str">
+        <v>damage:0.8</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ground_smash</v>
+        <v>lethal_strike</v>
       </c>
       <c r="B3" t="str">
-        <v>裂地击</v>
+        <v>致命一击</v>
       </c>
       <c r="C3" t="str">
         <v>dps</v>
       </c>
       <c r="D3" t="str">
-        <v>timer</v>
-      </c>
-      <c r="E3">
-        <v>8</v>
-      </c>
-      <c r="F3" t="str">
-        <v>nearest</v>
-      </c>
-      <c r="G3">
+        <v>active</v>
+      </c>
+      <c r="E3" t="str">
+        <v>attackCount</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3" t="str">
+        <v>single</v>
+      </c>
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3" t="str">
-        <v>damage:1.2</v>
+      <c r="I3">
+        <v>0</v>
       </c>
       <c r="J3" t="str">
+        <v>damage:3.5</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>lethal_strike</v>
+        <v>tank_stoneskin</v>
       </c>
       <c r="B4" t="str">
-        <v>致命一击</v>
+        <v>坚壁</v>
       </c>
       <c r="C4" t="str">
-        <v>dps</v>
+        <v>tank</v>
       </c>
       <c r="D4" t="str">
-        <v>attackCount</v>
-      </c>
-      <c r="E4">
-        <v>15</v>
+        <v>passive</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>single</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>damage:2.5</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>applyBuff:stone_skin</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>onHurt</v>
+      </c>
+      <c r="M4">
+        <v>0.15</v>
+      </c>
+      <c r="N4" t="str">
+        <v>self</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>healer_banner</v>
+      </c>
+      <c r="B5" t="str">
+        <v>战旗光环</v>
+      </c>
+      <c r="C5" t="str">
+        <v>healer</v>
+      </c>
+      <c r="D5" t="str">
+        <v>passive</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>applyBuff:war_banner</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>always</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5" t="str">
+        <v>team</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
   </ignoredErrors>
 </worksheet>
 </file>